--- a/sources/jack2_step4.xlsx
+++ b/sources/jack2_step4.xlsx
@@ -874,6 +874,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>19394d42-3833-4c2e-b3ec-46368a6b07eb</t>
@@ -926,6 +931,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>cb4f10b6-ee04-4947-a9bf-2a0a355cad60</t>
@@ -973,6 +983,11 @@
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>70ae82e4-7899-4172-9bbc-2145108370e7</t>
@@ -1018,6 +1033,11 @@
       <c r="N13" t="inlineStr">
         <is>
           <t>Pressing 1+3 from the side or back will result in a Hell Press, but it doesn't connect as a throw.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>052a3efc-5cdf-4aa6-9af6-a58c6ed3b504</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -5413,6 +5433,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>cedd2a7b-61d7-42fe-9349-42a2b1503d3f</t>
@@ -5440,6 +5465,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>46414757-6bbc-43ff-bcce-43bb3e815b75</t>
@@ -5467,6 +5497,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>66ed2d10-6ef0-489d-ad01-ab4680052d18</t>
@@ -5492,6 +5527,11 @@
       <c r="J105" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>bfdf582e-6190-406a-b25c-eee25e104050</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">

--- a/sources/jack2_step4.xlsx
+++ b/sources/jack2_step4.xlsx
@@ -4791,9 +4791,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <f>~3+4</f>
-        <v/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>– ~3+4</t>
+        </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4843,6 +4844,11 @@
       <c r="P87" t="inlineStr">
         <is>
           <t>1f37a24d-750f-4851-a2b5-a6b9a1b4ed26</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4885,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4922,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -4926,6 +4932,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -4973,7 +4984,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>421087d9-77e4-4344-95d3-0ffee0325022</t>
+          <t>3f1586e3-7d70-40ce-a201-943ab9917e0a</t>
         </is>
       </c>
     </row>
@@ -5028,6 +5039,11 @@
       <c r="A92" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
